--- a/SecComply_WhatsNew_Users.xlsx
+++ b/SecComply_WhatsNew_Users.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,23 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="001E293B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
@@ -113,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -135,11 +152,25 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,6 +215,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -551,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -818,6 +885,310 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Demo Type
+in Activity Filters</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>The 'Demo' activity type was missing from the filter tabs on the Activities page. There was no way to quickly view only your demo calls — it was hidden and couldn't be selected.</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>All activity types — including Demo — now appear as clickable filter tabs on the Activities page.
+You can now instantly filter the list to show only demo calls, discovery calls, tasks, or any other type.</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Activities page (left sidebar)
+→ filter tabs across the top of the list</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>1. Go to Activities in the left sidebar
+2. Click the 'Demo' tab to filter
+3. All logged demo activities appear
+4. Click 'All' to remove the filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>SOC 2 Compliance
+Workflow</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>There was no way to track clients going through a SOC 2 audit inside the CRM. Teams had to use separate spreadsheets to track where each client was in the process.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>A dedicated SOC 2 pipeline is now available with 7 built-in stages:
+• Scoping
+• Gap Assessment
+• Remediation
+• Readiness Review
+• Audit
+• Certified ✓
+• Not Pursued
+Clients are shown as cards on a kanban board. You can see active clients, completed certifications, and the total pipeline value at a glance.</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Left sidebar → Compliance → SOC 2 Workflow</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>1. Click 'SOC 2 Workflow' in the left sidebar under Compliance
+2. Click 'Add Client' to add a new client to the pipeline
+3. Fill in the deal form and save
+4. Drag cards between columns as the client progresses
+5. Click any card to open the full deal detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>DPDP Compliance
+Workflow</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>There was no way to track clients going through India's Digital Personal Data Protection (DPDP) compliance inside the CRM. This had to be managed outside the system.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>A dedicated DPDP pipeline is now available with 7 built-in stages:
+• Gap Assessment
+• Data Mapping
+• Policy Draft
+• Implementation
+• DPA Registration
+• Compliant ✓
+• Dropped
+Same kanban experience as SOC 2 — track all DPDP clients in one place with live stats on active, completed, and total pipeline value.</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Left sidebar → Compliance → DPDP Workflow</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>1. Click 'DPDP Workflow' in the left sidebar under Compliance
+2. Click 'Add Client' to add a new client
+3. Fill in the deal form and save
+4. Drag cards between stages as the engagement progresses
+5. Click any card to view full details</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Move a Prospect
+Into a Compliance
+Workflow</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>When a sales deal converted into a compliance engagement (SOC 2 or DPDP), there was no way to move it — you had to manually re-enter the client in the compliance pipeline from scratch.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Any open deal now has a 'Move to Workflow' button in the action bar.
+One click moves the prospect directly into either the SOC 2 or DPDP pipeline — no re-entry, no duplication. The deal retains all its history, contacts, and notes.</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Open any Deal/Prospect → action bar at the top right
+→ 'Move to Workflow' button</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>1. Open any deal from the Deals or Pipeline page
+2. Look for 'Move to Workflow' button in the top-right action bar
+3. Click it and choose 'SOC 2 Workflow' or 'DPDP Workflow'
+4. The deal moves instantly to the first stage of that compliance pipeline
+5. Find it under Compliance in the sidebar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Partner Referred
+Leads Tracking</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>When a partner referred a lead, there was no way inside the CRM to see which contacts or deals they had referred, or to understand how much revenue or how many wins came from each partner.</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>The Partners page now has two new tabs per partner:
+• Referred Leads — shows all contacts and deals that were referred by this partner, with their current status and referral date
+• Attribution — a stats summary showing:
+  - Total referred leads
+  - Open deals
+  - Won deals
+  - Won revenue
+  - Pipeline value
+  - Conversion rate %</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Left sidebar → Partners
+→ Expand any partner row
+→ Referred Leads tab or Attribution tab</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>1. Go to Partners in the left sidebar
+2. Click on any partner to expand their row
+3. Click the 'Referred Leads' tab to see all contacts and deals they referred
+4. Click the 'Attribution' tab to see revenue and conversion stats
+5. Referred contacts show status badge and referral date
+6. Referred deals show amount and pipeline stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Tag a Contact as
+Referred by a Partner</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>When adding a new contact who was introduced by a partner, there was no field to record who referred them or when. This attribution was lost and could not be tied back to the partner in reports.</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>When creating or editing a contact, selecting 'Referral' as the Source now reveals two new fields:
+• Referred by Partner — a dropdown of all your partner companies
+• Referral Date — when the referral was made
+Once saved, this contact automatically appears in the partner's Referred Leads tab.</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Contacts → Add Contact or click Edit on any contact
+→ Source field → select 'Referral'</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>1. Go to Contacts in the sidebar
+2. Click 'Add Contact' or open an existing contact and click Edit
+3. Scroll to the 'Source' dropdown and select 'Referral'
+4. Two new fields appear: 'Referred by Partner' and 'Referral Date'
+5. Select the partner company and enter the date
+6. Save — the contact will now appear in that partner's Referred Leads tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Daily Reminder
+Digest Email
+(One Per Day)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>The reminder email system was sending too many emails — sometimes multiple emails per hour per person. This made the emails easy to ignore and caused confusion about which reminders still needed action.</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Each user now receives exactly one consolidated reminder email per day, sent at 9:30 AM IST.
+This single email contains:
+• All overdue tasks assigned to you (from the Set Reminder feature on deals)
+• All prospects with no logged activity in the configured follow-up window
+Runal and Shivani are CC'd on every digest so the team always has visibility.
+No more repeat or duplicate emails — one clean daily summary.</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Your email inbox
+→ Subject: "CRM reminder digest: X due reminders + Y inactive prospects"
+→ Sent daily at 9:30 AM IST</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>1. Check your inbox each morning at 9:30 AM IST
+2. Open the daily CRM reminder digest email
+3. Review 'Due reminders' section for overdue tasks
+4. Review 'Inactive prospects' section for deals needing follow-up
+5. Log into the CRM and take action on each item
+6. Once a task is completed or activity is logged, it will not appear in the next day's digest</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
